--- a/copper.xlsx
+++ b/copper.xlsx
@@ -147,6 +147,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
       <t>《金正耀：《二里头青铜器的自然科学研究与夏文明探索》，《文物》</t>
     </r>
     <r>
@@ -5903,7 +5909,90 @@
     <t>白铜</t>
   </si>
   <si>
-    <t>《安志敏：《中国早期铜器的几个问题》，《考古学报》1981年第3期。》, 270页, 图一·3</t>
+    <r>
+      <t>《安志敏：《中国早期铜器的几个问题》，《考古学报》</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="1"/>
+      </rPr>
+      <t>1981</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>年第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="1"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>期。》</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="1"/>
+      </rPr>
+      <t>, 270</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>页</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>图一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="1"/>
+      </rPr>
+      <t>·3</t>
+    </r>
   </si>
   <si>
     <t>庙底沟类型</t>
@@ -6346,6 +6435,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>《中国社会科学院考古研究所：《胶县三里河》，文物出版社，</t>
     </r>
     <r>
@@ -6434,6 +6528,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>《中国社会科学院考古研究所：《胶县三里河》，文物出版社，</t>
     </r>
     <r>
@@ -7840,7 +7939,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7859,6 +7958,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -14273,7 +14375,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="198" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="198" ht="18" customHeight="1" spans="1:10">
       <c r="A198" s="1">
         <v>195</v>
       </c>
@@ -14305,7 +14407,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="199" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="199" ht="18" customHeight="1" spans="1:10">
       <c r="A199" s="1">
         <v>196</v>
       </c>
@@ -14337,7 +14439,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="200" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="200" ht="18" customHeight="1" spans="1:10">
       <c r="A200" s="1">
         <v>197</v>
       </c>
@@ -14369,7 +14471,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="201" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="201" ht="18" customHeight="1" spans="1:10">
       <c r="A201" s="1">
         <v>198</v>
       </c>
@@ -14401,7 +14503,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="202" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="202" ht="18" customHeight="1" spans="1:10">
       <c r="A202" s="1">
         <v>199</v>
       </c>
@@ -14429,7 +14531,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="203" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="203" ht="18" customHeight="1" spans="1:10">
       <c r="A203" s="1">
         <v>200</v>
       </c>
@@ -14461,7 +14563,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="204" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="204" ht="18" customHeight="1" spans="1:10">
       <c r="A204" s="1">
         <v>201</v>
       </c>
@@ -14493,7 +14595,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="205" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="205" ht="18" customHeight="1" spans="1:10">
       <c r="A205" s="1">
         <v>202</v>
       </c>
@@ -14525,7 +14627,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="206" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="206" ht="18" customHeight="1" spans="1:10">
       <c r="A206" s="1">
         <v>203</v>
       </c>
@@ -14553,7 +14655,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="207" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="207" ht="18" customHeight="1" spans="1:10">
       <c r="A207" s="1">
         <v>204</v>
       </c>
@@ -14581,7 +14683,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="208" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="208" ht="18" customHeight="1" spans="1:10">
       <c r="A208" s="1">
         <v>205</v>
       </c>
@@ -14609,7 +14711,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="209" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="209" ht="18" customHeight="1" spans="1:10">
       <c r="A209" s="1">
         <v>206</v>
       </c>
@@ -14641,7 +14743,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="210" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="210" ht="18" customHeight="1" spans="1:10">
       <c r="A210" s="1">
         <v>207</v>
       </c>
@@ -14673,7 +14775,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="211" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="211" ht="18" customHeight="1" spans="1:10">
       <c r="A211" s="1">
         <v>208</v>
       </c>
@@ -14701,7 +14803,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="212" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="212" ht="18" customHeight="1" spans="1:10">
       <c r="A212" s="1">
         <v>209</v>
       </c>
@@ -14731,7 +14833,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="213" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="213" ht="18" customHeight="1" spans="1:10">
       <c r="A213" s="1">
         <v>210</v>
       </c>
@@ -14757,7 +14859,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="214" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="214" ht="18" customHeight="1" spans="1:10">
       <c r="A214" s="1">
         <v>211</v>
       </c>
@@ -14783,7 +14885,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="215" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="215" ht="18" customHeight="1" spans="1:10">
       <c r="A215" s="1">
         <v>212</v>
       </c>
@@ -14809,7 +14911,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="216" ht="18" hidden="1" customHeight="1" spans="1:10">
+    <row r="216" ht="18" customHeight="1" spans="1:10">
       <c r="A216" s="1">
         <v>213</v>
       </c>
@@ -15001,7 +15103,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="223" ht="18" customHeight="1" spans="1:10">
+    <row r="223" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A223" s="1">
         <v>220</v>
       </c>
@@ -15033,7 +15135,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="224" ht="18" customHeight="1" spans="1:10">
+    <row r="224" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A224" s="1">
         <v>221</v>
       </c>
@@ -15059,7 +15161,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="225" ht="18" customHeight="1" spans="1:10">
+    <row r="225" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A225" s="1">
         <v>222</v>
       </c>
@@ -15087,7 +15189,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="226" ht="18" customHeight="1" spans="1:10">
+    <row r="226" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A226" s="1">
         <v>223</v>
       </c>
@@ -15113,7 +15215,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="227" ht="18" customHeight="1" spans="1:10">
+    <row r="227" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A227" s="1">
         <v>224</v>
       </c>
@@ -15141,7 +15243,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="228" ht="18" customHeight="1" spans="1:10">
+    <row r="228" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A228" s="1">
         <v>225</v>
       </c>
@@ -15171,7 +15273,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="229" ht="18" customHeight="1" spans="1:10">
+    <row r="229" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A229" s="1">
         <v>226</v>
       </c>
@@ -15199,7 +15301,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="230" ht="18" customHeight="1" spans="1:10">
+    <row r="230" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A230" s="1">
         <v>227</v>
       </c>
@@ -15227,7 +15329,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="231" ht="18" customHeight="1" spans="1:10">
+    <row r="231" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A231" s="1">
         <v>228</v>
       </c>
@@ -15253,7 +15355,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="232" ht="18" customHeight="1" spans="1:10">
+    <row r="232" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A232" s="1">
         <v>229</v>
       </c>
@@ -15279,7 +15381,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="233" ht="18" customHeight="1" spans="1:10">
+    <row r="233" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A233" s="1">
         <v>230</v>
       </c>
@@ -15305,7 +15407,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="234" ht="18" customHeight="1" spans="1:10">
+    <row r="234" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A234" s="1">
         <v>231</v>
       </c>
@@ -15331,7 +15433,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="235" ht="18" customHeight="1" spans="1:10">
+    <row r="235" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A235" s="1">
         <v>232</v>
       </c>
@@ -15357,7 +15459,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="236" ht="18" customHeight="1" spans="1:10">
+    <row r="236" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A236" s="1">
         <v>233</v>
       </c>
@@ -15385,7 +15487,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="237" ht="18" customHeight="1" spans="1:10">
+    <row r="237" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A237" s="1">
         <v>234</v>
       </c>
@@ -15415,7 +15517,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="238" ht="18" customHeight="1" spans="1:10">
+    <row r="238" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A238" s="1">
         <v>235</v>
       </c>
@@ -15445,7 +15547,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="239" ht="18" customHeight="1" spans="1:10">
+    <row r="239" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A239" s="1">
         <v>236</v>
       </c>
@@ -15475,7 +15577,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="240" ht="18" customHeight="1" spans="1:10">
+    <row r="240" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A240" s="1">
         <v>237</v>
       </c>
@@ -15505,7 +15607,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="241" ht="18" customHeight="1" spans="1:10">
+    <row r="241" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A241" s="1">
         <v>238</v>
       </c>
@@ -15533,7 +15635,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="242" ht="18" customHeight="1" spans="1:10">
+    <row r="242" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A242" s="1">
         <v>239</v>
       </c>
@@ -15561,7 +15663,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="243" ht="18" customHeight="1" spans="1:10">
+    <row r="243" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A243" s="1">
         <v>240</v>
       </c>
@@ -15591,7 +15693,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="244" ht="18" customHeight="1" spans="1:10">
+    <row r="244" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A244" s="1">
         <v>241</v>
       </c>
@@ -15623,7 +15725,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="245" ht="18" customHeight="1" spans="1:10">
+    <row r="245" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A245" s="1">
         <v>242</v>
       </c>
@@ -15651,7 +15753,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="246" ht="18" customHeight="1" spans="1:10">
+    <row r="246" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A246" s="1">
         <v>243</v>
       </c>
@@ -15683,7 +15785,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="247" ht="18" customHeight="1" spans="1:10">
+    <row r="247" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A247" s="1">
         <v>244</v>
       </c>
@@ -15715,7 +15817,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="248" ht="18" customHeight="1" spans="1:10">
+    <row r="248" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A248" s="1">
         <v>245</v>
       </c>
@@ -15745,7 +15847,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="249" ht="18" customHeight="1" spans="1:10">
+    <row r="249" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A249" s="1">
         <v>246</v>
       </c>
@@ -15775,7 +15877,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="250" ht="18" customHeight="1" spans="1:10">
+    <row r="250" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A250" s="1">
         <v>247</v>
       </c>
@@ -15807,7 +15909,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="251" ht="18" customHeight="1" spans="1:10">
+    <row r="251" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A251" s="1">
         <v>248</v>
       </c>
@@ -15837,7 +15939,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="252" ht="18" customHeight="1" spans="1:10">
+    <row r="252" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A252" s="1">
         <v>249</v>
       </c>
@@ -15867,7 +15969,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="253" ht="18" customHeight="1" spans="1:10">
+    <row r="253" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A253" s="1">
         <v>250</v>
       </c>
@@ -15897,7 +15999,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="254" ht="18" customHeight="1" spans="1:10">
+    <row r="254" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A254" s="1">
         <v>251</v>
       </c>
@@ -15929,7 +16031,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="255" ht="18" customHeight="1" spans="1:10">
+    <row r="255" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A255" s="1">
         <v>252</v>
       </c>
@@ -15959,7 +16061,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="256" ht="18" customHeight="1" spans="1:10">
+    <row r="256" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A256" s="1">
         <v>253</v>
       </c>
@@ -15987,7 +16089,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="257" ht="18" customHeight="1" spans="1:10">
+    <row r="257" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A257" s="1">
         <v>254</v>
       </c>
@@ -16019,7 +16121,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="258" ht="18" customHeight="1" spans="1:10">
+    <row r="258" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A258" s="1">
         <v>255</v>
       </c>
@@ -16049,7 +16151,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="259" ht="18" customHeight="1" spans="1:10">
+    <row r="259" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A259" s="1">
         <v>256</v>
       </c>
@@ -16077,7 +16179,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="260" ht="18" customHeight="1" spans="1:10">
+    <row r="260" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A260" s="1">
         <v>257</v>
       </c>
@@ -16109,7 +16211,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="261" ht="18" customHeight="1" spans="1:10">
+    <row r="261" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A261" s="1">
         <v>258</v>
       </c>
@@ -16139,7 +16241,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="262" ht="18" customHeight="1" spans="1:10">
+    <row r="262" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A262" s="1">
         <v>259</v>
       </c>
@@ -16169,7 +16271,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="263" ht="18" customHeight="1" spans="1:10">
+    <row r="263" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A263" s="1">
         <v>260</v>
       </c>
@@ -16199,7 +16301,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="264" ht="18" customHeight="1" spans="1:10">
+    <row r="264" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A264" s="1">
         <v>261</v>
       </c>
@@ -16229,7 +16331,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="265" ht="18" customHeight="1" spans="1:10">
+    <row r="265" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A265" s="1">
         <v>262</v>
       </c>
@@ -16261,7 +16363,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="266" ht="18" customHeight="1" spans="1:10">
+    <row r="266" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A266" s="1">
         <v>263</v>
       </c>
@@ -16291,7 +16393,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="267" ht="18" customHeight="1" spans="1:10">
+    <row r="267" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A267" s="1">
         <v>264</v>
       </c>
@@ -16323,7 +16425,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="268" ht="18" customHeight="1" spans="1:10">
+    <row r="268" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A268" s="1">
         <v>265</v>
       </c>
@@ -16353,7 +16455,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="269" ht="18" customHeight="1" spans="1:10">
+    <row r="269" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A269" s="1">
         <v>266</v>
       </c>
@@ -16381,7 +16483,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="270" ht="18" customHeight="1" spans="1:10">
+    <row r="270" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A270" s="1">
         <v>267</v>
       </c>
@@ -16409,7 +16511,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="271" ht="18" customHeight="1" spans="1:10">
+    <row r="271" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A271" s="1">
         <v>268</v>
       </c>
@@ -16437,7 +16539,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="272" ht="18" customHeight="1" spans="1:10">
+    <row r="272" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A272" s="1">
         <v>269</v>
       </c>
@@ -16469,7 +16571,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="273" ht="18" customHeight="1" spans="1:10">
+    <row r="273" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A273" s="1">
         <v>270</v>
       </c>
@@ -16499,7 +16601,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="274" ht="18" customHeight="1" spans="1:10">
+    <row r="274" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A274" s="1">
         <v>271</v>
       </c>
@@ -16531,7 +16633,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="275" ht="18" customHeight="1" spans="1:10">
+    <row r="275" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A275" s="1">
         <v>272</v>
       </c>
@@ -16559,7 +16661,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="276" ht="18" customHeight="1" spans="1:10">
+    <row r="276" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A276" s="1">
         <v>273</v>
       </c>
@@ -16585,7 +16687,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="277" ht="18" customHeight="1" spans="1:10">
+    <row r="277" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A277" s="1">
         <v>274</v>
       </c>
@@ -16611,7 +16713,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="278" ht="18" customHeight="1" spans="1:10">
+    <row r="278" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A278" s="1">
         <v>275</v>
       </c>
@@ -16637,7 +16739,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="279" ht="18" customHeight="1" spans="1:10">
+    <row r="279" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A279" s="1">
         <v>276</v>
       </c>
@@ -16663,7 +16765,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="280" ht="18" customHeight="1" spans="1:10">
+    <row r="280" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A280" s="1">
         <v>277</v>
       </c>
@@ -16691,7 +16793,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="281" ht="18" customHeight="1" spans="1:10">
+    <row r="281" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A281" s="1">
         <v>278</v>
       </c>
@@ -16717,7 +16819,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="282" ht="18" customHeight="1" spans="1:10">
+    <row r="282" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A282" s="1">
         <v>279</v>
       </c>
@@ -16743,7 +16845,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="283" ht="18" customHeight="1" spans="1:10">
+    <row r="283" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A283" s="1">
         <v>280</v>
       </c>
@@ -16771,7 +16873,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="284" ht="18" customHeight="1" spans="1:10">
+    <row r="284" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A284" s="1">
         <v>281</v>
       </c>
@@ -16799,7 +16901,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="285" ht="18" customHeight="1" spans="1:10">
+    <row r="285" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A285" s="1">
         <v>282</v>
       </c>
@@ -16825,7 +16927,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="286" ht="18" customHeight="1" spans="1:10">
+    <row r="286" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A286" s="1">
         <v>283</v>
       </c>
@@ -16857,7 +16959,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="287" ht="18" customHeight="1" spans="1:10">
+    <row r="287" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A287" s="1">
         <v>284</v>
       </c>
@@ -16889,7 +16991,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="288" ht="18" customHeight="1" spans="1:10">
+    <row r="288" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A288" s="1">
         <v>285</v>
       </c>
@@ -16919,7 +17021,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="289" ht="18" customHeight="1" spans="1:10">
+    <row r="289" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A289" s="1">
         <v>286</v>
       </c>
@@ -16947,7 +17049,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="290" ht="18" customHeight="1" spans="1:10">
+    <row r="290" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A290" s="1">
         <v>287</v>
       </c>
@@ -16973,7 +17075,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="291" ht="18" customHeight="1" spans="1:10">
+    <row r="291" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A291" s="1">
         <v>288</v>
       </c>
@@ -16999,7 +17101,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="292" ht="18" customHeight="1" spans="1:10">
+    <row r="292" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A292" s="1">
         <v>289</v>
       </c>
@@ -17025,7 +17127,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="293" ht="18" customHeight="1" spans="1:10">
+    <row r="293" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A293" s="1">
         <v>290</v>
       </c>
@@ -17057,7 +17159,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="294" ht="18" customHeight="1" spans="1:10">
+    <row r="294" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A294" s="1">
         <v>291</v>
       </c>
@@ -17085,7 +17187,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="295" ht="18" customHeight="1" spans="1:10">
+    <row r="295" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A295" s="1">
         <v>292</v>
       </c>
@@ -17113,7 +17215,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="296" ht="18" customHeight="1" spans="1:10">
+    <row r="296" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A296" s="1">
         <v>293</v>
       </c>
@@ -17141,7 +17243,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="297" ht="18" customHeight="1" spans="1:10">
+    <row r="297" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A297" s="1">
         <v>294</v>
       </c>
@@ -17169,7 +17271,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="298" ht="18" customHeight="1" spans="1:10">
+    <row r="298" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A298" s="1">
         <v>295</v>
       </c>
@@ -17197,7 +17299,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="299" ht="18" customHeight="1" spans="1:10">
+    <row r="299" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A299" s="1">
         <v>296</v>
       </c>
@@ -17225,7 +17327,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="300" ht="18" customHeight="1" spans="1:10">
+    <row r="300" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A300" s="1">
         <v>297</v>
       </c>
@@ -17253,7 +17355,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="301" ht="18" customHeight="1" spans="1:10">
+    <row r="301" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A301" s="1">
         <v>298</v>
       </c>
@@ -17281,7 +17383,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="302" ht="18" customHeight="1" spans="1:10">
+    <row r="302" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A302" s="1">
         <v>299</v>
       </c>
@@ -17309,7 +17411,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="303" ht="18" customHeight="1" spans="1:10">
+    <row r="303" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A303" s="1">
         <v>300</v>
       </c>
@@ -17335,7 +17437,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="304" ht="18" customHeight="1" spans="1:10">
+    <row r="304" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A304" s="1">
         <v>301</v>
       </c>
@@ -17361,7 +17463,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="305" ht="18" customHeight="1" spans="1:10">
+    <row r="305" ht="18" hidden="1" customHeight="1" spans="1:10">
       <c r="A305" s="1">
         <v>302</v>
       </c>
@@ -31365,7 +31467,7 @@
       <c r="I772" s="3" t="s">
         <v>1534</v>
       </c>
-      <c r="J772" s="3" t="s">
+      <c r="J772" s="8" t="s">
         <v>1535</v>
       </c>
       <c r="K772" s="3"/>
@@ -31430,7 +31532,7 @@
       </c>
       <c r="K774" s="3"/>
     </row>
-    <row r="775" ht="15" hidden="1" customHeight="1" spans="1:20">
+    <row r="775" ht="15" customHeight="1" spans="1:20">
       <c r="A775" s="1">
         <v>772</v>
       </c>
@@ -31690,19 +31792,19 @@
       </c>
       <c r="H783" s="5"/>
       <c r="I783" s="5"/>
-      <c r="J783" s="8" t="s">
+      <c r="J783" s="9" t="s">
         <v>1571</v>
       </c>
-      <c r="K783" s="8"/>
-      <c r="L783" s="8"/>
-      <c r="M783" s="9"/>
-      <c r="N783" s="8"/>
-      <c r="O783" s="9"/>
-      <c r="P783" s="8"/>
-      <c r="Q783" s="8"/>
-      <c r="R783" s="8"/>
-      <c r="S783" s="8"/>
-      <c r="T783" s="8"/>
+      <c r="K783" s="9"/>
+      <c r="L783" s="9"/>
+      <c r="M783" s="10"/>
+      <c r="N783" s="9"/>
+      <c r="O783" s="10"/>
+      <c r="P783" s="9"/>
+      <c r="Q783" s="9"/>
+      <c r="R783" s="9"/>
+      <c r="S783" s="9"/>
+      <c r="T783" s="9"/>
     </row>
     <row r="784" ht="15" hidden="1" customHeight="1" spans="1:20">
       <c r="A784" s="1">
@@ -31728,19 +31830,19 @@
       </c>
       <c r="H784" s="3"/>
       <c r="I784" s="3"/>
-      <c r="J784" s="10" t="s">
+      <c r="J784" s="11" t="s">
         <v>1574</v>
       </c>
-      <c r="K784" s="10"/>
-      <c r="L784" s="10"/>
-      <c r="M784" s="11"/>
-      <c r="N784" s="10"/>
-      <c r="O784" s="11"/>
-      <c r="P784" s="10"/>
-      <c r="Q784" s="10"/>
-      <c r="R784" s="10"/>
-      <c r="S784" s="10"/>
-      <c r="T784" s="10"/>
+      <c r="K784" s="11"/>
+      <c r="L784" s="11"/>
+      <c r="M784" s="12"/>
+      <c r="N784" s="11"/>
+      <c r="O784" s="12"/>
+      <c r="P784" s="11"/>
+      <c r="Q784" s="11"/>
+      <c r="R784" s="11"/>
+      <c r="S784" s="11"/>
+      <c r="T784" s="11"/>
     </row>
     <row r="785" ht="15" hidden="1" customHeight="1" spans="1:21">
       <c r="A785" s="1">
@@ -31768,19 +31870,19 @@
       <c r="I785" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J785" s="8" t="s">
+      <c r="J785" s="9" t="s">
         <v>1574</v>
       </c>
-      <c r="K785" s="8"/>
-      <c r="L785" s="8"/>
-      <c r="M785" s="9"/>
-      <c r="N785" s="8"/>
-      <c r="O785" s="9"/>
-      <c r="P785" s="8"/>
-      <c r="Q785" s="8"/>
-      <c r="R785" s="8"/>
-      <c r="S785" s="8"/>
-      <c r="T785" s="8"/>
+      <c r="K785" s="9"/>
+      <c r="L785" s="9"/>
+      <c r="M785" s="10"/>
+      <c r="N785" s="9"/>
+      <c r="O785" s="10"/>
+      <c r="P785" s="9"/>
+      <c r="Q785" s="9"/>
+      <c r="R785" s="9"/>
+      <c r="S785" s="9"/>
+      <c r="T785" s="9"/>
     </row>
     <row r="786" hidden="1" spans="1:21">
       <c r="A786" s="1">
@@ -31804,19 +31906,19 @@
       </c>
       <c r="H786" s="3"/>
       <c r="I786" s="3"/>
-      <c r="J786" s="12" t="s">
+      <c r="J786" s="13" t="s">
         <v>1577</v>
       </c>
-      <c r="K786" s="10"/>
-      <c r="L786" s="10"/>
-      <c r="M786" s="11"/>
-      <c r="N786" s="10"/>
-      <c r="O786" s="11"/>
-      <c r="P786" s="10"/>
-      <c r="Q786" s="10"/>
-      <c r="R786" s="10"/>
-      <c r="S786" s="10"/>
-      <c r="T786" s="10"/>
+      <c r="K786" s="11"/>
+      <c r="L786" s="11"/>
+      <c r="M786" s="12"/>
+      <c r="N786" s="11"/>
+      <c r="O786" s="12"/>
+      <c r="P786" s="11"/>
+      <c r="Q786" s="11"/>
+      <c r="R786" s="11"/>
+      <c r="S786" s="11"/>
+      <c r="T786" s="11"/>
       <c r="U786" s="4"/>
     </row>
     <row r="787" hidden="1" spans="1:21">
@@ -31847,19 +31949,19 @@
       <c r="I787" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J787" s="13" t="s">
+      <c r="J787" s="14" t="s">
         <v>1581</v>
       </c>
-      <c r="K787" s="8"/>
-      <c r="L787" s="8"/>
-      <c r="M787" s="9"/>
-      <c r="N787" s="8"/>
-      <c r="O787" s="9"/>
-      <c r="P787" s="8"/>
-      <c r="Q787" s="8"/>
-      <c r="R787" s="8"/>
-      <c r="S787" s="8"/>
-      <c r="T787" s="8"/>
+      <c r="K787" s="9"/>
+      <c r="L787" s="9"/>
+      <c r="M787" s="10"/>
+      <c r="N787" s="9"/>
+      <c r="O787" s="10"/>
+      <c r="P787" s="9"/>
+      <c r="Q787" s="9"/>
+      <c r="R787" s="9"/>
+      <c r="S787" s="9"/>
+      <c r="T787" s="9"/>
       <c r="U787" s="6"/>
     </row>
     <row r="788" hidden="1" spans="1:21">
@@ -31890,19 +31992,19 @@
       <c r="I788" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J788" s="12" t="s">
+      <c r="J788" s="13" t="s">
         <v>1583</v>
       </c>
-      <c r="K788" s="10"/>
-      <c r="L788" s="10"/>
-      <c r="M788" s="11"/>
-      <c r="N788" s="10"/>
-      <c r="O788" s="11"/>
-      <c r="P788" s="10"/>
-      <c r="Q788" s="10"/>
-      <c r="R788" s="10"/>
-      <c r="S788" s="10"/>
-      <c r="T788" s="10"/>
+      <c r="K788" s="11"/>
+      <c r="L788" s="11"/>
+      <c r="M788" s="12"/>
+      <c r="N788" s="11"/>
+      <c r="O788" s="12"/>
+      <c r="P788" s="11"/>
+      <c r="Q788" s="11"/>
+      <c r="R788" s="11"/>
+      <c r="S788" s="11"/>
+      <c r="T788" s="11"/>
       <c r="U788" s="4"/>
     </row>
     <row r="789" hidden="1" spans="1:21">
@@ -31927,20 +32029,20 @@
       </c>
       <c r="H789" s="5"/>
       <c r="I789" s="5"/>
-      <c r="J789" s="8"/>
-      <c r="K789" s="8"/>
-      <c r="L789" s="8"/>
-      <c r="M789" s="9"/>
-      <c r="N789" s="8"/>
-      <c r="O789" s="9"/>
-      <c r="P789" s="8"/>
-      <c r="Q789" s="8"/>
-      <c r="R789" s="8"/>
-      <c r="S789" s="8"/>
-      <c r="T789" s="8"/>
+      <c r="J789" s="9"/>
+      <c r="K789" s="9"/>
+      <c r="L789" s="9"/>
+      <c r="M789" s="10"/>
+      <c r="N789" s="9"/>
+      <c r="O789" s="10"/>
+      <c r="P789" s="9"/>
+      <c r="Q789" s="9"/>
+      <c r="R789" s="9"/>
+      <c r="S789" s="9"/>
+      <c r="T789" s="9"/>
       <c r="U789" s="6"/>
     </row>
-    <row r="790" hidden="1" spans="1:21">
+    <row r="790" spans="1:21">
       <c r="A790" s="1">
         <v>787</v>
       </c>
@@ -31968,22 +32070,22 @@
       <c r="I790" s="3" t="s">
         <v>1529</v>
       </c>
-      <c r="J790" s="14" t="s">
+      <c r="J790" s="15" t="s">
         <v>1590</v>
       </c>
-      <c r="K790" s="10"/>
-      <c r="L790" s="10"/>
-      <c r="M790" s="11"/>
-      <c r="N790" s="10"/>
-      <c r="O790" s="11"/>
-      <c r="P790" s="10"/>
-      <c r="Q790" s="10"/>
-      <c r="R790" s="10"/>
-      <c r="S790" s="10"/>
-      <c r="T790" s="10"/>
+      <c r="K790" s="11"/>
+      <c r="L790" s="11"/>
+      <c r="M790" s="12"/>
+      <c r="N790" s="11"/>
+      <c r="O790" s="12"/>
+      <c r="P790" s="11"/>
+      <c r="Q790" s="11"/>
+      <c r="R790" s="11"/>
+      <c r="S790" s="11"/>
+      <c r="T790" s="11"/>
       <c r="U790" s="4"/>
     </row>
-    <row r="791" hidden="1" spans="1:21">
+    <row r="791" spans="1:21">
       <c r="A791" s="1">
         <v>788</v>
       </c>
@@ -32011,22 +32113,22 @@
       <c r="I791" s="5" t="s">
         <v>1529</v>
       </c>
-      <c r="J791" s="15" t="s">
+      <c r="J791" s="16" t="s">
         <v>1592</v>
       </c>
-      <c r="K791" s="8"/>
-      <c r="L791" s="8"/>
-      <c r="M791" s="9"/>
-      <c r="N791" s="8"/>
-      <c r="O791" s="9"/>
-      <c r="P791" s="8"/>
-      <c r="Q791" s="8"/>
-      <c r="R791" s="8"/>
-      <c r="S791" s="8"/>
-      <c r="T791" s="8"/>
+      <c r="K791" s="9"/>
+      <c r="L791" s="9"/>
+      <c r="M791" s="10"/>
+      <c r="N791" s="9"/>
+      <c r="O791" s="10"/>
+      <c r="P791" s="9"/>
+      <c r="Q791" s="9"/>
+      <c r="R791" s="9"/>
+      <c r="S791" s="9"/>
+      <c r="T791" s="9"/>
       <c r="U791" s="6"/>
     </row>
-    <row r="792" hidden="1" spans="1:21">
+    <row r="792" spans="1:21">
       <c r="A792" s="1">
         <v>789</v>
       </c>
@@ -32048,22 +32150,22 @@
       </c>
       <c r="H792" s="3"/>
       <c r="I792" s="3"/>
-      <c r="J792" s="12" t="s">
+      <c r="J792" s="13" t="s">
         <v>1594</v>
       </c>
-      <c r="K792" s="10"/>
-      <c r="L792" s="10"/>
-      <c r="M792" s="11"/>
-      <c r="N792" s="10"/>
-      <c r="O792" s="11"/>
-      <c r="P792" s="10"/>
-      <c r="Q792" s="10"/>
-      <c r="R792" s="10"/>
-      <c r="S792" s="10"/>
-      <c r="T792" s="10"/>
+      <c r="K792" s="11"/>
+      <c r="L792" s="11"/>
+      <c r="M792" s="12"/>
+      <c r="N792" s="11"/>
+      <c r="O792" s="12"/>
+      <c r="P792" s="11"/>
+      <c r="Q792" s="11"/>
+      <c r="R792" s="11"/>
+      <c r="S792" s="11"/>
+      <c r="T792" s="11"/>
       <c r="U792" s="4"/>
     </row>
-    <row r="793" hidden="1" spans="1:21">
+    <row r="793" spans="1:21">
       <c r="A793" s="1">
         <v>790</v>
       </c>
@@ -32087,22 +32189,22 @@
       </c>
       <c r="H793" s="5"/>
       <c r="I793" s="5"/>
-      <c r="J793" s="13" t="s">
+      <c r="J793" s="14" t="s">
         <v>1598</v>
       </c>
-      <c r="K793" s="8"/>
-      <c r="L793" s="8"/>
-      <c r="M793" s="9"/>
-      <c r="N793" s="8"/>
-      <c r="O793" s="9"/>
-      <c r="P793" s="8"/>
-      <c r="Q793" s="8"/>
-      <c r="R793" s="8"/>
-      <c r="S793" s="8"/>
-      <c r="T793" s="8"/>
+      <c r="K793" s="9"/>
+      <c r="L793" s="9"/>
+      <c r="M793" s="10"/>
+      <c r="N793" s="9"/>
+      <c r="O793" s="10"/>
+      <c r="P793" s="9"/>
+      <c r="Q793" s="9"/>
+      <c r="R793" s="9"/>
+      <c r="S793" s="9"/>
+      <c r="T793" s="9"/>
       <c r="U793" s="6"/>
     </row>
-    <row r="794" hidden="1" spans="1:21">
+    <row r="794" spans="1:21">
       <c r="A794" s="1">
         <v>791</v>
       </c>
@@ -32112,10 +32214,10 @@
       <c r="C794" s="3" t="s">
         <v>1586</v>
       </c>
-      <c r="D794" s="8" t="s">
+      <c r="D794" s="9" t="s">
         <v>1595</v>
       </c>
-      <c r="E794" s="9" t="s">
+      <c r="E794" s="10" t="s">
         <v>1599</v>
       </c>
       <c r="F794" s="3" t="s">
@@ -32126,22 +32228,22 @@
       </c>
       <c r="H794" s="3"/>
       <c r="I794" s="3"/>
-      <c r="J794" s="12" t="s">
+      <c r="J794" s="13" t="s">
         <v>1601</v>
       </c>
-      <c r="K794" s="10"/>
-      <c r="L794" s="10"/>
-      <c r="M794" s="11"/>
-      <c r="N794" s="10"/>
-      <c r="O794" s="11"/>
-      <c r="P794" s="10"/>
-      <c r="Q794" s="10"/>
-      <c r="R794" s="10"/>
-      <c r="S794" s="10"/>
-      <c r="T794" s="10"/>
+      <c r="K794" s="11"/>
+      <c r="L794" s="11"/>
+      <c r="M794" s="12"/>
+      <c r="N794" s="11"/>
+      <c r="O794" s="12"/>
+      <c r="P794" s="11"/>
+      <c r="Q794" s="11"/>
+      <c r="R794" s="11"/>
+      <c r="S794" s="11"/>
+      <c r="T794" s="11"/>
       <c r="U794" s="4"/>
     </row>
-    <row r="795" hidden="1" spans="1:21">
+    <row r="795" spans="1:21">
       <c r="A795" s="1">
         <v>792</v>
       </c>
@@ -32151,7 +32253,7 @@
       <c r="C795" s="5" t="s">
         <v>1586</v>
       </c>
-      <c r="D795" s="5" t="s">
+      <c r="D795" s="7" t="s">
         <v>1602</v>
       </c>
       <c r="E795" s="6"/>
@@ -32165,22 +32267,22 @@
       <c r="I795" s="5" t="s">
         <v>1529</v>
       </c>
-      <c r="J795" s="13" t="s">
+      <c r="J795" s="14" t="s">
         <v>1601</v>
       </c>
-      <c r="K795" s="8"/>
-      <c r="L795" s="8"/>
-      <c r="M795" s="9"/>
-      <c r="N795" s="8"/>
-      <c r="O795" s="9"/>
-      <c r="P795" s="8"/>
-      <c r="Q795" s="8"/>
-      <c r="R795" s="8"/>
-      <c r="S795" s="8"/>
-      <c r="T795" s="8"/>
+      <c r="K795" s="9"/>
+      <c r="L795" s="9"/>
+      <c r="M795" s="10"/>
+      <c r="N795" s="9"/>
+      <c r="O795" s="10"/>
+      <c r="P795" s="9"/>
+      <c r="Q795" s="9"/>
+      <c r="R795" s="9"/>
+      <c r="S795" s="9"/>
+      <c r="T795" s="9"/>
       <c r="U795" s="6"/>
     </row>
-    <row r="796" hidden="1" spans="1:21">
+    <row r="796" spans="1:21">
       <c r="A796" s="1">
         <v>793</v>
       </c>
@@ -32202,22 +32304,22 @@
       </c>
       <c r="H796" s="3"/>
       <c r="I796" s="3"/>
-      <c r="J796" s="12" t="s">
+      <c r="J796" s="13" t="s">
         <v>1601</v>
       </c>
-      <c r="K796" s="10"/>
-      <c r="L796" s="10"/>
-      <c r="M796" s="11"/>
-      <c r="N796" s="10"/>
-      <c r="O796" s="11"/>
-      <c r="P796" s="10"/>
-      <c r="Q796" s="10"/>
-      <c r="R796" s="10"/>
-      <c r="S796" s="10"/>
-      <c r="T796" s="10"/>
+      <c r="K796" s="11"/>
+      <c r="L796" s="11"/>
+      <c r="M796" s="12"/>
+      <c r="N796" s="11"/>
+      <c r="O796" s="12"/>
+      <c r="P796" s="11"/>
+      <c r="Q796" s="11"/>
+      <c r="R796" s="11"/>
+      <c r="S796" s="11"/>
+      <c r="T796" s="11"/>
       <c r="U796" s="4"/>
     </row>
-    <row r="797" hidden="1" spans="1:21">
+    <row r="797" spans="1:21">
       <c r="A797" s="1">
         <v>794</v>
       </c>
@@ -32239,19 +32341,19 @@
       </c>
       <c r="H797" s="5"/>
       <c r="I797" s="5"/>
-      <c r="J797" s="13" t="s">
+      <c r="J797" s="14" t="s">
         <v>1601</v>
       </c>
-      <c r="K797" s="8"/>
-      <c r="L797" s="8"/>
-      <c r="M797" s="9"/>
-      <c r="N797" s="8"/>
-      <c r="O797" s="9"/>
-      <c r="P797" s="8"/>
-      <c r="Q797" s="8"/>
-      <c r="R797" s="8"/>
-      <c r="S797" s="8"/>
-      <c r="T797" s="8"/>
+      <c r="K797" s="9"/>
+      <c r="L797" s="9"/>
+      <c r="M797" s="10"/>
+      <c r="N797" s="9"/>
+      <c r="O797" s="10"/>
+      <c r="P797" s="9"/>
+      <c r="Q797" s="9"/>
+      <c r="R797" s="9"/>
+      <c r="S797" s="9"/>
+      <c r="T797" s="9"/>
       <c r="U797" s="6"/>
     </row>
     <row r="798" hidden="1" spans="1:21">
@@ -32282,19 +32384,19 @@
       <c r="I798" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J798" s="12" t="s">
+      <c r="J798" s="13" t="s">
         <v>1608</v>
       </c>
-      <c r="K798" s="10"/>
-      <c r="L798" s="10"/>
-      <c r="M798" s="11"/>
-      <c r="N798" s="10"/>
-      <c r="O798" s="11"/>
-      <c r="P798" s="10"/>
-      <c r="Q798" s="10"/>
-      <c r="R798" s="10"/>
-      <c r="S798" s="10"/>
-      <c r="T798" s="10"/>
+      <c r="K798" s="11"/>
+      <c r="L798" s="11"/>
+      <c r="M798" s="12"/>
+      <c r="N798" s="11"/>
+      <c r="O798" s="12"/>
+      <c r="P798" s="11"/>
+      <c r="Q798" s="11"/>
+      <c r="R798" s="11"/>
+      <c r="S798" s="11"/>
+      <c r="T798" s="11"/>
       <c r="U798" s="4"/>
     </row>
     <row r="799" hidden="1" spans="1:21">
@@ -32319,19 +32421,19 @@
       </c>
       <c r="H799" s="5"/>
       <c r="I799" s="5"/>
-      <c r="J799" s="13" t="s">
+      <c r="J799" s="14" t="s">
         <v>1610</v>
       </c>
-      <c r="K799" s="8"/>
-      <c r="L799" s="8"/>
-      <c r="M799" s="9"/>
-      <c r="N799" s="8"/>
-      <c r="O799" s="9"/>
-      <c r="P799" s="8"/>
-      <c r="Q799" s="8"/>
-      <c r="R799" s="8"/>
-      <c r="S799" s="8"/>
-      <c r="T799" s="8"/>
+      <c r="K799" s="9"/>
+      <c r="L799" s="9"/>
+      <c r="M799" s="10"/>
+      <c r="N799" s="9"/>
+      <c r="O799" s="10"/>
+      <c r="P799" s="9"/>
+      <c r="Q799" s="9"/>
+      <c r="R799" s="9"/>
+      <c r="S799" s="9"/>
+      <c r="T799" s="9"/>
       <c r="U799" s="6"/>
     </row>
     <row r="800" hidden="1" spans="1:21">
@@ -32362,19 +32464,19 @@
       <c r="I800" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="J800" s="12" t="s">
+      <c r="J800" s="13" t="s">
         <v>1612</v>
       </c>
-      <c r="K800" s="10"/>
-      <c r="L800" s="10"/>
-      <c r="M800" s="11"/>
-      <c r="N800" s="10"/>
-      <c r="O800" s="11"/>
-      <c r="P800" s="10"/>
-      <c r="Q800" s="10"/>
-      <c r="R800" s="10"/>
-      <c r="S800" s="10"/>
-      <c r="T800" s="10"/>
+      <c r="K800" s="11"/>
+      <c r="L800" s="11"/>
+      <c r="M800" s="12"/>
+      <c r="N800" s="11"/>
+      <c r="O800" s="12"/>
+      <c r="P800" s="11"/>
+      <c r="Q800" s="11"/>
+      <c r="R800" s="11"/>
+      <c r="S800" s="11"/>
+      <c r="T800" s="11"/>
       <c r="U800" s="4"/>
     </row>
     <row r="801" hidden="1" spans="1:21">
@@ -32403,19 +32505,19 @@
       <c r="I801" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J801" s="13" t="s">
+      <c r="J801" s="14" t="s">
         <v>1614</v>
       </c>
-      <c r="K801" s="8"/>
-      <c r="L801" s="8"/>
-      <c r="M801" s="9"/>
-      <c r="N801" s="8"/>
-      <c r="O801" s="9"/>
-      <c r="P801" s="8"/>
-      <c r="Q801" s="8"/>
-      <c r="R801" s="8"/>
-      <c r="S801" s="8"/>
-      <c r="T801" s="8"/>
+      <c r="K801" s="9"/>
+      <c r="L801" s="9"/>
+      <c r="M801" s="10"/>
+      <c r="N801" s="9"/>
+      <c r="O801" s="10"/>
+      <c r="P801" s="9"/>
+      <c r="Q801" s="9"/>
+      <c r="R801" s="9"/>
+      <c r="S801" s="9"/>
+      <c r="T801" s="9"/>
       <c r="U801" s="6"/>
     </row>
     <row r="802" hidden="1" spans="1:21">
@@ -32444,56 +32546,66 @@
       <c r="I802" s="3" t="s">
         <v>1617</v>
       </c>
-      <c r="J802" s="12" t="s">
+      <c r="J802" s="13" t="s">
         <v>1618</v>
       </c>
-      <c r="K802" s="10"/>
-      <c r="L802" s="10"/>
-      <c r="M802" s="11"/>
-      <c r="N802" s="10"/>
-      <c r="O802" s="11"/>
-      <c r="P802" s="10"/>
-      <c r="Q802" s="10"/>
-      <c r="R802" s="10"/>
-      <c r="S802" s="10"/>
-      <c r="T802" s="10"/>
+      <c r="K802" s="11"/>
+      <c r="L802" s="11"/>
+      <c r="M802" s="12"/>
+      <c r="N802" s="11"/>
+      <c r="O802" s="12"/>
+      <c r="P802" s="11"/>
+      <c r="Q802" s="11"/>
+      <c r="R802" s="11"/>
+      <c r="S802" s="11"/>
+      <c r="T802" s="11"/>
       <c r="U802" s="4"/>
     </row>
     <row r="803" spans="1:21">
       <c r="I803" s="5"/>
-      <c r="J803" s="8"/>
-      <c r="K803" s="8"/>
-      <c r="L803" s="8"/>
-      <c r="M803" s="9"/>
-      <c r="N803" s="8"/>
-      <c r="O803" s="9"/>
-      <c r="P803" s="8"/>
-      <c r="Q803" s="8"/>
-      <c r="R803" s="8"/>
-      <c r="S803" s="8"/>
-      <c r="T803" s="8"/>
+      <c r="J803" s="9"/>
+      <c r="K803" s="9"/>
+      <c r="L803" s="9"/>
+      <c r="M803" s="10"/>
+      <c r="N803" s="9"/>
+      <c r="O803" s="10"/>
+      <c r="P803" s="9"/>
+      <c r="Q803" s="9"/>
+      <c r="R803" s="9"/>
+      <c r="S803" s="9"/>
+      <c r="T803" s="9"/>
       <c r="U803" s="6"/>
     </row>
     <row r="804" spans="1:21">
       <c r="I804" s="3"/>
-      <c r="J804" s="10"/>
-      <c r="K804" s="10"/>
-      <c r="L804" s="10"/>
-      <c r="M804" s="11"/>
-      <c r="N804" s="10"/>
-      <c r="O804" s="11"/>
-      <c r="P804" s="10"/>
-      <c r="Q804" s="10"/>
-      <c r="R804" s="10"/>
-      <c r="S804" s="10"/>
-      <c r="T804" s="10"/>
+      <c r="J804" s="11"/>
+      <c r="K804" s="11"/>
+      <c r="L804" s="11"/>
+      <c r="M804" s="12"/>
+      <c r="N804" s="11"/>
+      <c r="O804" s="12"/>
+      <c r="P804" s="11"/>
+      <c r="Q804" s="11"/>
+      <c r="R804" s="11"/>
+      <c r="S804" s="11"/>
+      <c r="T804" s="11"/>
       <c r="U804" s="4"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B3:J802" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="0">
+    <filterColumn colId="2">
       <filters>
-        <filter val="燕山地区"/>
+        <filter val="山东长岛北长山岛店子"/>
+        <filter val="山东诸城呈子"/>
+        <filter val="山东泰安大汶口"/>
+        <filter val="山东胶县三里河"/>
+        <filter val="山东青州郝家庄"/>
+        <filter val="山东临沂大范庄"/>
+        <filter val="山东牟平照格庄"/>
+        <filter val="山东栖霞杨家圈"/>
+        <filter val="山东邹平丁公"/>
+        <filter val="山东日照尧王城"/>
+        <filter val="山东泗水尹家城"/>
       </filters>
     </filterColumn>
     <extLst/>
